--- a/branches/fix/hygiene-parity/ValueSet-mii-vs-dokument-sct-dokument-kategorie.xlsx
+++ b/branches/fix/hygiene-parity/ValueSet-mii-vs-dokument-sct-dokument-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:56:18+00:00</t>
+    <t>2026-09-04T15:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
